--- a/hira_material_automation/output/monthly/202601_202606__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__all_suture_anchor__040021__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:23:48</t>
+          <t>2026-06-14T22:17:08</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>320f7f71768906e629888ee2ab870fe9006478340460bafc32373e8de6207cfc</t>
+          <t>1c4da7da97cb7cac56e5f90024745c7f07d923e5e00883b176ef7a19edfe8d24</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__all_suture_anchor__040021__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:08</t>
+          <t>2026-06-24T22:21:55</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1c4da7da97cb7cac56e5f90024745c7f07d923e5e00883b176ef7a19edfe8d24</t>
+          <t>bc389b98511d425c71d91255a2c155d85a6cacb7cc6dc06d75fa8b58fd1f36d9</t>
         </is>
       </c>
     </row>
